--- a/Data/FlightPlan/FPL_30OCT26.xlsx
+++ b/Data/FlightPlan/FPL_30OCT26.xlsx
@@ -293,6 +293,9 @@
     <t>23:45</t>
   </si>
   <si>
+    <t>23:58</t>
+  </si>
+  <si>
     <t>01:40</t>
   </si>
   <si>
@@ -386,6 +389,12 @@
     <t>06:55</t>
   </si>
   <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
     <t>VN-A528</t>
   </si>
   <si>
@@ -431,6 +440,9 @@
     <t>22:25</t>
   </si>
   <si>
+    <t>00:02</t>
+  </si>
+  <si>
     <t>VN-A529</t>
   </si>
   <si>
@@ -581,9 +593,6 @@
     <t>PXU</t>
   </si>
   <si>
-    <t>07:45</t>
-  </si>
-  <si>
     <t>07:38</t>
   </si>
   <si>
@@ -626,6 +635,9 @@
     <t>00:15</t>
   </si>
   <si>
+    <t>00:33</t>
+  </si>
+  <si>
     <t>VN-A542</t>
   </si>
   <si>
@@ -734,7 +746,7 @@
     <t>23:55</t>
   </si>
   <si>
-    <t>23:58</t>
+    <t>23:50</t>
   </si>
   <si>
     <t>VN-A551</t>
@@ -866,9 +878,6 @@
     <t>23:00</t>
   </si>
   <si>
-    <t>23:13</t>
-  </si>
-  <si>
     <t>VN-A575</t>
   </si>
   <si>
@@ -1109,9 +1118,6 @@
     <t>19:01</t>
   </si>
   <si>
-    <t>00:55</t>
-  </si>
-  <si>
     <t>VN-A639</t>
   </si>
   <si>
@@ -1133,7 +1139,7 @@
     <t>18:35</t>
   </si>
   <si>
-    <t>23:54</t>
+    <t>00:07</t>
   </si>
   <si>
     <t>00:20</t>
@@ -1328,6 +1334,9 @@
     <t>01:30</t>
   </si>
   <si>
+    <t>01:51</t>
+  </si>
+  <si>
     <t>04:10</t>
   </si>
   <si>
@@ -1646,6 +1655,9 @@
     <t>05:35</t>
   </si>
   <si>
+    <t>05:24</t>
+  </si>
+  <si>
     <t>VN-A685</t>
   </si>
   <si>
@@ -1727,9 +1739,6 @@
     <t>16:19</t>
   </si>
   <si>
-    <t>05:36</t>
-  </si>
-  <si>
     <t>VN-A812</t>
   </si>
   <si>
@@ -1793,13 +1802,13 @@
     <t>00:04</t>
   </si>
   <si>
-    <t>06:36</t>
+    <t>06:48</t>
   </si>
   <si>
     <t>Total Record(s): 349</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 30, 2026 21:58</t>
+    <t xml:space="preserve">Generated on  Oct 30, 2026 22:41</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3216,7 +3225,9 @@
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
+      <c t="s" r="M33" s="7">
+        <v>94</v>
+      </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c t="s" r="A34" s="6">
@@ -3242,10 +3253,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I34" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -3278,7 +3289,7 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
@@ -3287,10 +3298,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H36" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J36" s="7">
         <v>41</v>
@@ -3298,7 +3309,7 @@
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c t="s" r="M36" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
@@ -3313,22 +3324,22 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G37" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="H37" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -3348,7 +3359,7 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
@@ -3357,13 +3368,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H38" s="8">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -3396,7 +3407,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -3408,15 +3419,15 @@
         <v>39</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
       <c t="s" r="M40" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -3431,7 +3442,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -3446,12 +3457,12 @@
         <v>69</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c t="s" r="M41" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
@@ -3466,7 +3477,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -3475,13 +3486,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H42" s="8">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -3501,22 +3512,22 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="H43" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -3549,7 +3560,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -3561,15 +3572,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c t="s" r="M45" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -3584,7 +3595,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3593,18 +3604,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I46" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c t="s" r="M46" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -3619,19 +3630,19 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H47" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J47" s="7">
         <v>44</v>
@@ -3639,7 +3650,7 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c t="s" r="M47" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -3654,7 +3665,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3663,17 +3674,21 @@
         <v>16</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>124</v>
-      </c>
-      <c r="K48" s="7"/>
+        <v>125</v>
+      </c>
+      <c t="s" r="K48" s="7">
+        <v>126</v>
+      </c>
       <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
+      <c t="s" r="M48" s="7">
+        <v>127</v>
+      </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="6"/>
@@ -3702,27 +3717,27 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
       <c t="s" r="M50" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
@@ -3737,27 +3752,27 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c t="s" r="H51" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c t="s" r="M51" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -3772,19 +3787,19 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G52" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H52" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J52" s="7">
         <v>70</v>
@@ -3792,7 +3807,7 @@
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c t="s" r="M52" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
@@ -3807,7 +3822,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3816,10 +3831,10 @@
         <v>36</v>
       </c>
       <c t="s" r="H53" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J53" s="7">
         <v>58</v>
@@ -3827,7 +3842,7 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3842,13 +3857,13 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G54" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H54" s="8">
         <v>36</v>
@@ -3862,7 +3877,7 @@
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c t="s" r="M54" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
@@ -3877,7 +3892,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3886,17 +3901,19 @@
         <v>36</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c t="s" r="J55" s="7">
         <v>93</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
+      <c t="s" r="M55" s="7">
+        <v>143</v>
+      </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="6"/>
@@ -3925,7 +3942,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3937,17 +3954,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="K57" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L57" s="7"/>
       <c t="s" r="M57" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
@@ -3962,7 +3979,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3974,15 +3991,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c t="s" r="M58" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -3997,7 +4014,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -4006,13 +4023,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H59" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -4045,7 +4062,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -4054,10 +4071,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="J61" s="7">
         <v>50</v>
@@ -4065,7 +4082,7 @@
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
       <c t="s" r="M61" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -4080,27 +4097,27 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c t="s" r="M62" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -4115,7 +4132,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -4124,10 +4141,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>69</v>
@@ -4135,7 +4152,7 @@
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c t="s" r="M63" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
@@ -4150,22 +4167,22 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G64" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H64" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -4185,7 +4202,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -4235,7 +4252,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -4244,18 +4261,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="I67" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -4270,27 +4287,27 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -4305,7 +4322,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -4314,18 +4331,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -4340,27 +4357,27 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H70" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -4375,7 +4392,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4384,7 +4401,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c t="s" r="I71" s="7">
         <v>73</v>
@@ -4395,7 +4412,7 @@
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -4410,22 +4427,22 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c t="s" r="H72" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -4458,7 +4475,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4470,15 +4487,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4493,7 +4510,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4508,12 +4525,12 @@
         <v>67</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4528,7 +4545,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4537,18 +4554,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4563,27 +4580,27 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4598,7 +4615,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4607,18 +4624,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="I78" s="7">
         <v>86</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4633,13 +4650,13 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>36</v>
@@ -4653,7 +4670,7 @@
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4683,7 +4700,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4692,18 +4709,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="I81" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4718,19 +4735,19 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G82" s="8">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="H82" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J82" s="7">
         <v>50</v>
@@ -4753,7 +4770,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4765,15 +4782,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4788,7 +4805,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4800,15 +4817,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4823,7 +4840,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4832,18 +4849,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4858,27 +4875,27 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="H86" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4893,7 +4910,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4908,12 +4925,12 @@
         <v>25</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4928,7 +4945,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4940,14 +4957,16 @@
         <v>16</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
-      <c r="M88" s="7"/>
+      <c t="s" r="M88" s="7">
+        <v>208</v>
+      </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="6"/>
@@ -4976,13 +4995,13 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H90" s="8">
         <v>35</v>
@@ -4996,7 +5015,7 @@
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -5011,7 +5030,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -5026,12 +5045,12 @@
         <v>24</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -5046,7 +5065,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -5058,7 +5077,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>84</v>
@@ -5066,7 +5085,7 @@
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -5081,7 +5100,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -5093,7 +5112,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>87</v>
@@ -5101,7 +5120,7 @@
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -5116,7 +5135,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -5131,12 +5150,12 @@
         <v>58</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -5151,7 +5170,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -5163,7 +5182,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>37</v>
@@ -5199,7 +5218,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -5208,18 +5227,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5234,27 +5253,27 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -5269,7 +5288,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5278,18 +5297,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I99" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -5304,27 +5323,27 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -5339,7 +5358,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -5348,20 +5367,20 @@
         <v>36</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c t="s" r="K101" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -5376,13 +5395,13 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>36</v>
@@ -5391,14 +5410,14 @@
         <v>57</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c t="s" r="K102" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5413,7 +5432,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5425,17 +5444,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>61</v>
       </c>
       <c t="s" r="K103" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5450,7 +5469,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5462,17 +5481,17 @@
         <v>36</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c t="s" r="K104" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5498,11 +5517,11 @@
         <v>6849</v>
       </c>
       <c t="s" r="C106" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5522,7 +5541,7 @@
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -5537,7 +5556,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5549,7 +5568,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>51</v>
@@ -5557,7 +5576,7 @@
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5572,7 +5591,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5581,18 +5600,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5607,19 +5626,19 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>71</v>
@@ -5627,7 +5646,7 @@
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5642,7 +5661,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5662,7 +5681,7 @@
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5677,7 +5696,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5692,12 +5711,12 @@
         <v>92</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5727,7 +5746,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5736,18 +5755,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5762,27 +5781,27 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5797,27 +5816,27 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5832,27 +5851,27 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5867,7 +5886,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5876,20 +5895,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>70</v>
       </c>
       <c t="s" r="K117" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5904,29 +5923,29 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="K118" s="7">
         <v>75</v>
       </c>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5956,19 +5975,19 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>69</v>
@@ -5991,7 +6010,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -6000,18 +6019,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -6026,27 +6045,27 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -6061,7 +6080,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -6070,18 +6089,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c t="s" r="I123" s="7">
         <v>73</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -6096,22 +6115,22 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -6144,19 +6163,19 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>33</v>
@@ -6164,7 +6183,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6179,7 +6198,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -6188,10 +6207,10 @@
         <v>36</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>21</v>
@@ -6199,7 +6218,7 @@
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -6214,27 +6233,27 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -6249,7 +6268,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6258,10 +6277,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>84</v>
@@ -6269,7 +6288,7 @@
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6284,19 +6303,19 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>25</v>
@@ -6319,7 +6338,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6328,18 +6347,18 @@
         <v>82</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6369,7 +6388,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6381,15 +6400,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -6404,7 +6423,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6419,12 +6438,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6439,7 +6458,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6448,18 +6467,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -6474,19 +6493,19 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>58</v>
@@ -6494,7 +6513,7 @@
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6509,7 +6528,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6518,18 +6537,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>285</v>
+        <v>102</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6555,31 +6574,31 @@
         <v>6843</v>
       </c>
       <c t="s" r="C139" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c t="s" r="M139" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
@@ -6590,11 +6609,11 @@
         <v>6843</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6606,17 +6625,17 @@
         <v>35</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="K140" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6631,7 +6650,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6643,7 +6662,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>58</v>
@@ -6651,7 +6670,7 @@
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6681,7 +6700,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6693,15 +6712,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6716,7 +6735,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6731,12 +6750,12 @@
         <v>67</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6751,7 +6770,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6763,15 +6782,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6786,7 +6805,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6798,15 +6817,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6821,7 +6840,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6830,18 +6849,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6856,13 +6875,13 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>36</v>
@@ -6871,12 +6890,12 @@
         <v>71</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6891,7 +6910,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6900,18 +6919,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6926,13 +6945,13 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>36</v>
@@ -6941,7 +6960,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6970,33 +6989,33 @@
         <v>6863</v>
       </c>
       <c t="s" r="C152" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c t="s" r="H152" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c t="s" r="K152" s="7">
         <v>20</v>
       </c>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -7007,11 +7026,11 @@
         <v>6863</v>
       </c>
       <c t="s" r="C153" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -7020,20 +7039,20 @@
         <v>36</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c t="s" r="K153" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -7044,23 +7063,23 @@
         <v>6868</v>
       </c>
       <c t="s" r="C154" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>57</v>
@@ -7070,7 +7089,7 @@
       </c>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7081,11 +7100,11 @@
         <v>6868</v>
       </c>
       <c t="s" r="C155" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -7094,20 +7113,20 @@
         <v>36</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c t="s" r="I155" s="7">
         <v>71</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c t="s" r="K155" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -7118,29 +7137,29 @@
         <v>6869</v>
       </c>
       <c t="s" r="C156" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="K156" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
@@ -7174,29 +7193,29 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="K158" s="7">
         <v>38</v>
       </c>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -7211,7 +7230,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7220,18 +7239,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c t="s" r="I159" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7246,22 +7265,22 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -7294,27 +7313,27 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -7329,7 +7348,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -7341,15 +7360,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7364,7 +7383,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7376,15 +7395,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7399,7 +7418,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7411,15 +7430,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7434,7 +7453,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7446,15 +7465,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7484,7 +7503,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7496,15 +7515,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7519,7 +7538,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7534,12 +7553,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7554,7 +7573,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7566,15 +7585,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7589,7 +7608,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7601,15 +7620,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7624,7 +7643,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7636,17 +7655,17 @@
         <v>35</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c t="s" r="K172" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7661,7 +7680,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7673,17 +7692,17 @@
         <v>36</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="K173" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7698,7 +7717,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7710,17 +7729,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c t="s" r="K174" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7750,7 +7769,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7762,15 +7781,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7785,7 +7804,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7800,12 +7819,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7820,7 +7839,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7835,7 +7854,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7868,7 +7887,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7877,18 +7896,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7903,27 +7922,27 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7938,7 +7957,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7950,7 +7969,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>68</v>
@@ -7958,7 +7977,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7973,7 +7992,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7985,15 +8004,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -8008,7 +8027,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -8020,7 +8039,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="J184" s="7">
         <v>86</v>
@@ -8028,7 +8047,7 @@
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -8043,7 +8062,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -8055,7 +8074,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>71</v>
@@ -8063,7 +8082,7 @@
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -8078,7 +8097,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -8087,18 +8106,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8113,27 +8132,27 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8163,7 +8182,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8175,15 +8194,15 @@
         <v>56</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -8198,7 +8217,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -8210,15 +8229,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8233,7 +8252,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8245,15 +8264,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8268,7 +8287,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8277,7 +8296,7 @@
         <v>36</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="I192" s="7">
         <v>53</v>
@@ -8290,7 +8309,7 @@
       </c>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8305,25 +8324,25 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>44</v>
       </c>
       <c t="s" r="K193" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
@@ -8342,7 +8361,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8351,13 +8370,13 @@
         <v>36</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>366</v>
+        <v>126</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -8390,7 +8409,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8399,18 +8418,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8425,13 +8444,13 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>36</v>
@@ -8440,12 +8459,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8460,7 +8479,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8469,18 +8488,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8495,27 +8514,27 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8530,7 +8549,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8539,7 +8558,7 @@
         <v>36</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I200" s="7">
         <v>84</v>
@@ -8552,7 +8571,7 @@
       </c>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8567,29 +8586,29 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c t="s" r="K201" s="7">
         <v>25</v>
       </c>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8604,7 +8623,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8619,12 +8638,12 @@
         <v>90</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8639,7 +8658,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8651,10 +8670,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -8687,7 +8706,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8699,15 +8718,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8722,7 +8741,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8737,12 +8756,12 @@
         <v>21</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8757,7 +8776,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8766,18 +8785,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8792,27 +8811,27 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8827,7 +8846,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8839,7 +8858,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>92</v>
@@ -8847,7 +8866,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8877,7 +8896,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8886,18 +8905,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="I211" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8912,27 +8931,27 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8947,7 +8966,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8956,10 +8975,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>83</v>
@@ -8967,7 +8986,7 @@
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8982,27 +9001,27 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -9017,7 +9036,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -9037,7 +9056,7 @@
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -9052,7 +9071,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -9061,13 +9080,13 @@
         <v>36</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -9085,22 +9104,22 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -9133,7 +9152,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9142,18 +9161,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9168,27 +9187,27 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9203,7 +9222,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9215,15 +9234,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9238,7 +9257,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -9247,18 +9266,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -9273,19 +9292,19 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>43</v>
@@ -9293,7 +9312,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9323,27 +9342,27 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9358,27 +9377,27 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9393,27 +9412,27 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -9428,22 +9447,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I228" s="7">
         <v>29</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -9476,7 +9495,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9485,10 +9504,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>19</v>
@@ -9511,13 +9530,13 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>16</v>
@@ -9526,12 +9545,12 @@
         <v>20</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9546,7 +9565,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9555,10 +9574,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>68</v>
@@ -9566,7 +9585,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9581,13 +9600,13 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>16</v>
@@ -9596,12 +9615,12 @@
         <v>69</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9616,7 +9635,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9625,10 +9644,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>55</v>
@@ -9636,7 +9655,7 @@
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9651,27 +9670,27 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9686,7 +9705,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9698,7 +9717,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>61</v>
@@ -9706,7 +9725,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9721,7 +9740,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9736,7 +9755,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9769,7 +9788,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9781,15 +9800,15 @@
         <v>39</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9804,7 +9823,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9816,7 +9835,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>43</v>
@@ -9824,7 +9843,7 @@
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9839,7 +9858,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9851,15 +9870,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9874,7 +9893,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9886,15 +9905,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9924,7 +9943,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9933,18 +9952,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9959,19 +9978,19 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>83</v>
@@ -9979,7 +9998,7 @@
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9994,7 +10013,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -10003,18 +10022,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -10029,27 +10048,27 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -10064,7 +10083,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -10076,10 +10095,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -10112,7 +10131,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -10124,15 +10143,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -10147,7 +10166,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -10156,18 +10175,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -10182,27 +10201,27 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -10217,7 +10236,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -10226,18 +10245,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10252,27 +10271,27 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10287,7 +10306,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -10296,18 +10315,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10322,27 +10341,27 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10372,7 +10391,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10381,18 +10400,18 @@
         <v>23</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10407,27 +10426,27 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10442,19 +10461,19 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>57</v>
@@ -10462,7 +10481,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10477,7 +10496,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10486,17 +10505,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
-      <c r="M261" s="7"/>
+      <c t="s" r="M261" s="7">
+        <v>441</v>
+      </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
       <c t="s" r="A262" s="6">
@@ -10510,22 +10531,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10558,7 +10579,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10567,10 +10588,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>24</v>
@@ -10578,7 +10599,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10593,13 +10614,13 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>35</v>
@@ -10608,12 +10629,12 @@
         <v>80</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10628,7 +10649,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10637,18 +10658,18 @@
         <v>35</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10663,13 +10684,13 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>16</v>
@@ -10683,7 +10704,7 @@
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10698,7 +10719,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10713,12 +10734,12 @@
         <v>44</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10733,7 +10754,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10742,10 +10763,10 @@
         <v>36</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>366</v>
+        <v>126</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>48</v>
@@ -10781,22 +10802,22 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -10816,7 +10837,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -10825,18 +10846,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10851,27 +10872,27 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10901,7 +10922,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -10913,15 +10934,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10936,7 +10957,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -10951,12 +10972,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10971,7 +10992,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -10980,18 +11001,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -11006,19 +11027,19 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>90</v>
@@ -11026,7 +11047,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -11056,27 +11077,27 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11087,11 +11108,11 @@
         <v>380</v>
       </c>
       <c t="s" r="C281" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -11100,18 +11121,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="I281" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -11126,13 +11147,13 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>16</v>
@@ -11146,7 +11167,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11161,7 +11182,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -11170,18 +11191,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -11196,27 +11217,27 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -11231,7 +11252,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -11240,13 +11261,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -11266,27 +11287,27 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11301,7 +11322,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -11310,18 +11331,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="I287" s="7">
         <v>89</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11336,13 +11357,13 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>16</v>
@@ -11351,12 +11372,12 @@
         <v>44</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11371,7 +11392,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -11383,17 +11404,17 @@
         <v>36</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c t="s" r="K289" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11423,7 +11444,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -11435,15 +11456,15 @@
         <v>66</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11458,7 +11479,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -11470,15 +11491,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11493,7 +11514,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -11502,10 +11523,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>44</v>
@@ -11513,7 +11534,7 @@
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11543,27 +11564,27 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11578,27 +11599,27 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11613,27 +11634,27 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11663,7 +11684,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -11675,10 +11696,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -11698,7 +11719,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11707,20 +11728,20 @@
         <v>36</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c t="s" r="K300" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11735,29 +11756,29 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="K301" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11772,7 +11793,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11781,18 +11802,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11807,22 +11828,22 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -11855,7 +11876,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11864,18 +11885,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11890,13 +11911,13 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>36</v>
@@ -11905,12 +11926,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11925,7 +11946,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11934,18 +11955,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11960,27 +11981,27 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11995,7 +12016,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -12007,17 +12028,17 @@
         <v>35</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>57</v>
       </c>
       <c t="s" r="K309" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -12032,7 +12053,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -12047,14 +12068,14 @@
         <v>71</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="K310" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -12084,7 +12105,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -12093,18 +12114,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -12119,27 +12140,27 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -12154,7 +12175,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -12163,18 +12184,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -12189,19 +12210,19 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>69</v>
@@ -12209,7 +12230,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12224,7 +12245,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -12233,18 +12254,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12259,13 +12280,13 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>16</v>
@@ -12274,12 +12295,12 @@
         <v>27</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -12309,7 +12330,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -12318,18 +12339,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12344,16 +12365,16 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>22</v>
@@ -12364,7 +12385,7 @@
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12379,27 +12400,27 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>69</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12414,27 +12435,27 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12449,13 +12470,13 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>36</v>
@@ -12464,7 +12485,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -12482,7 +12503,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -12491,13 +12512,13 @@
         <v>36</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -12530,7 +12551,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12542,15 +12563,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12565,7 +12586,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12574,18 +12595,18 @@
         <v>82</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12600,27 +12621,27 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12635,7 +12656,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12647,15 +12668,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12670,7 +12691,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -12682,15 +12703,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12705,7 +12726,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12717,10 +12738,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -12740,7 +12761,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -12749,18 +12770,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c t="s" r="I332" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12775,22 +12796,22 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -12823,7 +12844,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12832,18 +12853,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12858,27 +12879,27 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -12893,7 +12914,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -12913,7 +12934,7 @@
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12928,7 +12949,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12940,7 +12961,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>93</v>
@@ -12978,7 +12999,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12987,18 +13008,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -13013,13 +13034,13 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>36</v>
@@ -13028,12 +13049,12 @@
         <v>41</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -13048,7 +13069,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -13066,11 +13087,11 @@
         <v>92</v>
       </c>
       <c t="s" r="K342" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13085,7 +13106,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -13097,13 +13118,13 @@
         <v>36</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="K343" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
@@ -13137,7 +13158,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -13146,13 +13167,13 @@
         <v>36</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -13172,19 +13193,19 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>21</v>
@@ -13192,7 +13213,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13207,7 +13228,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -13216,10 +13237,10 @@
         <v>36</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>83</v>
@@ -13227,7 +13248,7 @@
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -13242,19 +13263,19 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>84</v>
@@ -13262,7 +13283,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -13277,7 +13298,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -13286,7 +13307,7 @@
         <v>36</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c t="s" r="I349" s="7">
         <v>54</v>
@@ -13297,7 +13318,7 @@
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -13312,27 +13333,27 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13347,7 +13368,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -13359,10 +13380,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -13395,7 +13416,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -13404,18 +13425,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c t="s" r="I353" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13430,13 +13451,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>16</v>
@@ -13445,12 +13466,12 @@
         <v>21</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13465,7 +13486,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -13474,18 +13495,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13500,22 +13521,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -13535,7 +13556,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -13544,18 +13565,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13570,22 +13591,22 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -13618,7 +13639,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13627,20 +13648,20 @@
         <v>36</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="K360" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13655,27 +13676,27 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13690,27 +13711,27 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13740,22 +13761,22 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -13775,7 +13796,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13784,18 +13805,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13810,27 +13831,27 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13845,7 +13866,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13857,15 +13878,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13880,7 +13901,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13889,18 +13910,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>284</v>
+        <v>463</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13915,22 +13936,22 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13963,7 +13984,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13972,18 +13993,18 @@
         <v>23</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13998,26 +14019,28 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>23</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
-      <c r="M372" s="7"/>
+      <c t="s" r="M372" s="7">
+        <v>548</v>
+      </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
       <c r="A373" s="6"/>
@@ -14046,7 +14069,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -14061,12 +14084,12 @@
         <v>21</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -14081,7 +14104,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -14090,7 +14113,7 @@
         <v>36</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c t="s" r="I375" s="7">
         <v>53</v>
@@ -14101,7 +14124,7 @@
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -14116,13 +14139,13 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>36</v>
@@ -14131,12 +14154,12 @@
         <v>55</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -14147,11 +14170,11 @@
         <v>6293</v>
       </c>
       <c t="s" r="C377" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -14160,18 +14183,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14182,26 +14205,26 @@
         <v>6294</v>
       </c>
       <c t="s" r="C378" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -14234,7 +14257,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -14243,18 +14266,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14269,13 +14292,13 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>16</v>
@@ -14284,12 +14307,12 @@
         <v>48</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14304,7 +14327,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -14316,15 +14339,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -14339,7 +14362,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -14351,7 +14374,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>53</v>
@@ -14359,7 +14382,7 @@
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14374,7 +14397,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14383,10 +14406,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>70</v>
@@ -14394,7 +14417,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14409,27 +14432,27 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14444,22 +14467,22 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
+        <v>556</v>
+      </c>
+      <c r="F386" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G386" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H386" s="8">
         <v>552</v>
       </c>
-      <c r="F386" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G386" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H386" s="8">
-        <v>548</v>
-      </c>
       <c t="s" r="I386" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -14477,22 +14500,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
+        <v>556</v>
+      </c>
+      <c r="F387" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G387" s="8">
         <v>552</v>
       </c>
-      <c r="F387" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G387" s="8">
-        <v>548</v>
-      </c>
       <c t="s" r="H387" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -14525,7 +14548,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14534,18 +14557,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14560,19 +14583,19 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>69</v>
@@ -14580,7 +14603,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14595,7 +14618,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14604,10 +14627,10 @@
         <v>36</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>57</v>
@@ -14615,7 +14638,7 @@
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14630,13 +14653,13 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>36</v>
@@ -14645,12 +14668,12 @@
         <v>87</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14665,7 +14688,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14677,17 +14700,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c t="s" r="K393" s="7">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14717,7 +14740,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14726,18 +14749,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="I395" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14752,27 +14775,27 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14787,7 +14810,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14799,15 +14822,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14822,7 +14845,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14837,12 +14860,12 @@
         <v>57</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14857,7 +14880,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14869,10 +14892,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14905,27 +14928,27 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14940,27 +14963,27 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I402" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>572</v>
+        <v>547</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14990,13 +15013,13 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>16</v>
@@ -15005,12 +15028,12 @@
         <v>24</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -15025,7 +15048,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -15040,12 +15063,12 @@
         <v>71</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -15075,7 +15098,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -15087,15 +15110,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -15110,7 +15133,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -15119,18 +15142,18 @@
         <v>35</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -15145,22 +15168,22 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -15189,26 +15212,26 @@
         <v>6876</v>
       </c>
       <c t="s" r="C411" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -15224,26 +15247,26 @@
         <v>6877</v>
       </c>
       <c t="s" r="C412" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -15276,7 +15299,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -15285,18 +15308,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15311,27 +15334,27 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15361,7 +15384,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -15370,18 +15393,18 @@
         <v>35</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -15396,13 +15419,13 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>35</v>
@@ -15411,12 +15434,12 @@
         <v>87</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15446,7 +15469,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -15458,15 +15481,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15481,7 +15504,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -15493,15 +15516,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15516,7 +15539,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -15525,18 +15548,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c t="s" r="I422" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15551,32 +15574,32 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c t="s" r="A424" s="9">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B424" s="9"/>
       <c r="C424" s="9"/>
@@ -15596,7 +15619,7 @@
     <row r="425" ht="66" customHeight="1"/>
     <row r="426" ht="16.5" customHeight="1">
       <c t="s" r="A426" s="10">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B426" s="10"/>
       <c r="C426" s="10"/>
@@ -15609,7 +15632,7 @@
       <c r="J426" s="10"/>
       <c r="K426" s="10"/>
       <c t="s" r="L426" s="11">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="M426" s="11"/>
       <c r="N426" s="11"/>
